--- a/pensum/ok09/OK09_Budsjettering_Regneark_Budsjett.xlsx
+++ b/pensum/ok09/OK09_Budsjettering_Regneark_Budsjett.xlsx
@@ -1278,12 +1278,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1291,11 +1295,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1303,7 +1307,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1311,15 +1315,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1327,7 +1331,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1339,31 +1343,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1371,55 +1375,55 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1687,230 +1691,230 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="7" t="n">
+        <v>982650</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>1800000</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>2520000</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>3092250</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="10" t="n">
         <f aca="false">B6*1.25</f>
         <v>2250000</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="11" t="n">
         <f aca="false">MAX(0,(30-B7)/30)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="10" t="n">
         <f aca="false">B12*B13</f>
         <v>750000</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="10" t="n">
         <f aca="false">B8+B14</f>
         <v>3270000</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="10" t="n">
         <f aca="false">B15-B9</f>
         <v>177750</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <f aca="false">B5+B16</f>
-        <v>1177750</v>
-      </c>
-      <c r="C18" s="7" t="s">
+        <v>1160400</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="10" t="n">
         <f aca="false">B12-B14</f>
         <v>1500000</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="str">
+      <c r="A22" s="14" t="str">
         <f aca="false">"Ved månedsslutt står det "&amp;TEXT(ROUND(B18,0),"#,##0")&amp;" kroner på konto. Av januarsalget er "&amp;TEXT(ROUND(B19,0),"#,##0")&amp;" kroner tjent, men ikke betalt ennå."</f>
-        <v>Ved månedsslutt står det 1,177,750 kroner på konto. Av januarsalget er 1,500,000 kroner tjent, men ikke betalt ennå.</v>
-      </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
+        <v>Ved månedsslutt står det 1,160,400 kroner på konto. Av januarsalget er 1,500,000 kroner tjent, men ikke betalt ennå.</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1939,314 +1943,314 @@
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="20" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="23" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="20" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="20" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="17" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2269,829 +2273,829 @@
   <dimension ref="A1:O37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="N5" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="23" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="24" t="n">
         <f aca="false">2</f>
         <v>2</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="24" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="24" t="n">
         <f aca="false">4</f>
         <v>4</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="24" t="n">
         <f aca="false">5</f>
         <v>5</v>
       </c>
-      <c r="H6" s="23" t="n">
+      <c r="H6" s="24" t="n">
         <f aca="false">6</f>
         <v>6</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="24" t="n">
         <f aca="false">7</f>
         <v>7</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="24" t="n">
         <f aca="false">8</f>
         <v>8</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="24" t="n">
         <f aca="false">9</f>
         <v>9</v>
       </c>
-      <c r="L6" s="23" t="n">
+      <c r="L6" s="24" t="n">
         <f aca="false">10</f>
         <v>10</v>
       </c>
-      <c r="M6" s="23" t="n">
+      <c r="M6" s="24" t="n">
         <f aca="false">11</f>
         <v>11</v>
       </c>
-      <c r="N6" s="23" t="n">
+      <c r="N6" s="24" t="n">
         <f aca="false">12</f>
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="25" t="n">
         <f aca="false">SUM(C7:N7)</f>
         <v>24000000</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <v>1800000</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <v>2100000</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>2200000</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <v>2100000</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <v>2000000</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="26" t="n">
         <v>2000000</v>
       </c>
-      <c r="I7" s="25" t="n">
+      <c r="I7" s="26" t="n">
         <v>1200000</v>
       </c>
-      <c r="J7" s="25" t="n">
+      <c r="J7" s="26" t="n">
         <v>1900000</v>
       </c>
-      <c r="K7" s="25" t="n">
+      <c r="K7" s="26" t="n">
         <v>2100000</v>
       </c>
-      <c r="L7" s="25" t="n">
+      <c r="L7" s="26" t="n">
         <v>2200000</v>
       </c>
-      <c r="M7" s="25" t="n">
+      <c r="M7" s="26" t="n">
         <v>2300000</v>
       </c>
-      <c r="N7" s="25" t="n">
+      <c r="N7" s="26" t="n">
         <v>2100000</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O7" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="27" t="n">
         <v>0.625</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="O8" s="20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="25" t="n">
         <f aca="false">SUM(C9:N9)</f>
         <v>9000000</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <f aca="false">C7*(1-$B$8)</f>
         <v>675000</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="28" t="n">
         <f aca="false">D7*(1-$B$8)</f>
         <v>787500</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="28" t="n">
         <f aca="false">E7*(1-$B$8)</f>
         <v>825000</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="28" t="n">
         <f aca="false">F7*(1-$B$8)</f>
         <v>787500</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="28" t="n">
         <f aca="false">G7*(1-$B$8)</f>
         <v>750000</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="28" t="n">
         <f aca="false">H7*(1-$B$8)</f>
         <v>750000</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="28" t="n">
         <f aca="false">I7*(1-$B$8)</f>
         <v>450000</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="28" t="n">
         <f aca="false">J7*(1-$B$8)</f>
         <v>712500</v>
       </c>
-      <c r="K9" s="27" t="n">
+      <c r="K9" s="28" t="n">
         <f aca="false">K7*(1-$B$8)</f>
         <v>787500</v>
       </c>
-      <c r="L9" s="27" t="n">
+      <c r="L9" s="28" t="n">
         <f aca="false">L7*(1-$B$8)</f>
         <v>825000</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="28" t="n">
         <f aca="false">M7*(1-$B$8)</f>
         <v>862500</v>
       </c>
-      <c r="N9" s="27" t="n">
+      <c r="N9" s="28" t="n">
         <f aca="false">N7*(1-$B$8)</f>
         <v>787500</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="20" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <v>700000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="27" t="n">
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="27" t="n">
         <v>0.141</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <f aca="false">B10*12*(1+B11)*(1+B12)</f>
         <v>10734528</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="O13" s="20" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <v>680000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <v>1500000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="25" t="n">
         <f aca="false">B7</f>
         <v>24000000</v>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C19" s="28" t="n">
         <f aca="false">C7</f>
         <v>1800000</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="28" t="n">
         <f aca="false">D7</f>
         <v>2100000</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="28" t="n">
         <f aca="false">E7</f>
         <v>2200000</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="28" t="n">
         <f aca="false">F7</f>
         <v>2100000</v>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G19" s="28" t="n">
         <f aca="false">G7</f>
         <v>2000000</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="28" t="n">
         <f aca="false">H7</f>
         <v>2000000</v>
       </c>
-      <c r="I19" s="27" t="n">
+      <c r="I19" s="28" t="n">
         <f aca="false">I7</f>
         <v>1200000</v>
       </c>
-      <c r="J19" s="27" t="n">
+      <c r="J19" s="28" t="n">
         <f aca="false">J7</f>
         <v>1900000</v>
       </c>
-      <c r="K19" s="27" t="n">
+      <c r="K19" s="28" t="n">
         <f aca="false">K7</f>
         <v>2100000</v>
       </c>
-      <c r="L19" s="27" t="n">
+      <c r="L19" s="28" t="n">
         <f aca="false">L7</f>
         <v>2200000</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="28" t="n">
         <f aca="false">M7</f>
         <v>2300000</v>
       </c>
-      <c r="N19" s="27" t="n">
+      <c r="N19" s="28" t="n">
         <f aca="false">N7</f>
         <v>2100000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="28" t="n">
         <f aca="false">B9</f>
         <v>9000000</v>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="28" t="n">
         <f aca="false">C9</f>
         <v>675000</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="28" t="n">
         <f aca="false">D9</f>
         <v>787500</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <f aca="false">E9</f>
         <v>825000</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="28" t="n">
         <f aca="false">F9</f>
         <v>787500</v>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="28" t="n">
         <f aca="false">G9</f>
         <v>750000</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <f aca="false">H9</f>
         <v>750000</v>
       </c>
-      <c r="I20" s="27" t="n">
+      <c r="I20" s="28" t="n">
         <f aca="false">I9</f>
         <v>450000</v>
       </c>
-      <c r="J20" s="27" t="n">
+      <c r="J20" s="28" t="n">
         <f aca="false">J9</f>
         <v>712500</v>
       </c>
-      <c r="K20" s="27" t="n">
+      <c r="K20" s="28" t="n">
         <f aca="false">K9</f>
         <v>787500</v>
       </c>
-      <c r="L20" s="27" t="n">
+      <c r="L20" s="28" t="n">
         <f aca="false">L9</f>
         <v>825000</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="28" t="n">
         <f aca="false">M9</f>
         <v>862500</v>
       </c>
-      <c r="N20" s="27" t="n">
+      <c r="N20" s="28" t="n">
         <f aca="false">N9</f>
         <v>787500</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="28" t="n">
         <f aca="false">B13</f>
         <v>10734528</v>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="I21" s="27" t="n">
+      <c r="I21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="J21" s="27" t="n">
+      <c r="J21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="K21" s="27" t="n">
+      <c r="K21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="L21" s="27" t="n">
+      <c r="L21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
-      <c r="N21" s="27" t="n">
+      <c r="N21" s="28" t="n">
         <f aca="false">$B$13/12</f>
         <v>894544</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B22" s="28" t="n">
         <f aca="false">B14</f>
         <v>680000</v>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="D22" s="27" t="n">
+      <c r="D22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="I22" s="27" t="n">
+      <c r="I22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="J22" s="27" t="n">
+      <c r="J22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="K22" s="27" t="n">
+      <c r="K22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="L22" s="27" t="n">
+      <c r="L22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="N22" s="27" t="n">
+      <c r="N22" s="28" t="n">
         <f aca="false">$B$14/12</f>
         <v>56666.6666666667</v>
       </c>
-      <c r="O22" s="19" t="s">
+      <c r="O22" s="20" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="28" t="n">
         <f aca="false">B15</f>
         <v>1500000</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="G23" s="27" t="n">
+      <c r="G23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="I23" s="27" t="n">
+      <c r="I23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="J23" s="27" t="n">
+      <c r="J23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="K23" s="27" t="n">
+      <c r="K23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="L23" s="27" t="n">
+      <c r="L23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
-      <c r="N23" s="27" t="n">
+      <c r="N23" s="28" t="n">
         <f aca="false">$B$15/12</f>
         <v>125000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="25" t="n">
         <f aca="false">SUM(B20:B23)</f>
         <v>21914528</v>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="28" t="n">
         <f aca="false">SUM(C20:C23)</f>
         <v>1751210.66666667</v>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D24" s="28" t="n">
         <f aca="false">SUM(D20:D23)</f>
         <v>1863710.66666667</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="28" t="n">
         <f aca="false">SUM(E20:E23)</f>
         <v>1901210.66666667</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="28" t="n">
         <f aca="false">SUM(F20:F23)</f>
         <v>1863710.66666667</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="28" t="n">
         <f aca="false">SUM(G20:G23)</f>
         <v>1826210.66666667</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="28" t="n">
         <f aca="false">SUM(H20:H23)</f>
         <v>1826210.66666667</v>
       </c>
-      <c r="I24" s="27" t="n">
+      <c r="I24" s="28" t="n">
         <f aca="false">SUM(I20:I23)</f>
         <v>1526210.66666667</v>
       </c>
-      <c r="J24" s="27" t="n">
+      <c r="J24" s="28" t="n">
         <f aca="false">SUM(J20:J23)</f>
         <v>1788710.66666667</v>
       </c>
-      <c r="K24" s="27" t="n">
+      <c r="K24" s="28" t="n">
         <f aca="false">SUM(K20:K23)</f>
         <v>1863710.66666667</v>
       </c>
-      <c r="L24" s="27" t="n">
+      <c r="L24" s="28" t="n">
         <f aca="false">SUM(L20:L23)</f>
         <v>1901210.66666667</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="28" t="n">
         <f aca="false">SUM(M20:M23)</f>
         <v>1938710.66666667</v>
       </c>
-      <c r="N24" s="27" t="n">
+      <c r="N24" s="28" t="n">
         <f aca="false">SUM(N20:N23)</f>
         <v>1863710.66666667</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="25" t="n">
         <f aca="false">B19-B24</f>
         <v>2085472</v>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="25" t="n">
         <f aca="false">C19-C24</f>
         <v>48789.3333333333</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <f aca="false">D19-D24</f>
         <v>236289.333333333</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <f aca="false">E19-E24</f>
         <v>298789.333333333</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <f aca="false">F19-F24</f>
         <v>236289.333333333</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="25" t="n">
         <f aca="false">G19-G24</f>
         <v>173789.333333333</v>
       </c>
-      <c r="H25" s="24" t="n">
+      <c r="H25" s="25" t="n">
         <f aca="false">H19-H24</f>
         <v>173789.333333333</v>
       </c>
-      <c r="I25" s="24" t="n">
+      <c r="I25" s="25" t="n">
         <f aca="false">I19-I24</f>
         <v>-326210.666666667</v>
       </c>
-      <c r="J25" s="24" t="n">
+      <c r="J25" s="25" t="n">
         <f aca="false">J19-J24</f>
         <v>111289.333333333</v>
       </c>
-      <c r="K25" s="24" t="n">
+      <c r="K25" s="25" t="n">
         <f aca="false">K19-K24</f>
         <v>236289.333333333</v>
       </c>
-      <c r="L25" s="24" t="n">
+      <c r="L25" s="25" t="n">
         <f aca="false">L19-L24</f>
         <v>298789.333333333</v>
       </c>
-      <c r="M25" s="24" t="n">
+      <c r="M25" s="25" t="n">
         <f aca="false">M19-M24</f>
         <v>361289.333333333</v>
       </c>
-      <c r="N25" s="24" t="n">
+      <c r="N25" s="25" t="n">
         <f aca="false">N19-N24</f>
         <v>236289.333333333</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="29" t="n">
         <f aca="false">B25/B19</f>
         <v>0.0868946666666667</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="30" t="n">
         <f aca="false">C25/C19</f>
         <v>0.0271051851851851</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="30" t="n">
         <f aca="false">D25/D19</f>
         <v>0.11251873015873</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="30" t="n">
         <f aca="false">E25/E19</f>
         <v>0.135813333333333</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="30" t="n">
         <f aca="false">F25/F19</f>
         <v>0.11251873015873</v>
       </c>
-      <c r="G26" s="29" t="n">
+      <c r="G26" s="30" t="n">
         <f aca="false">G25/G19</f>
         <v>0.0868946666666666</v>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="H26" s="30" t="n">
         <f aca="false">H25/H19</f>
         <v>0.0868946666666666</v>
       </c>
-      <c r="I26" s="29" t="n">
+      <c r="I26" s="30" t="n">
         <f aca="false">I25/I19</f>
         <v>-0.271842222222222</v>
       </c>
-      <c r="J26" s="29" t="n">
+      <c r="J26" s="30" t="n">
         <f aca="false">J25/J19</f>
         <v>0.0585733333333333</v>
       </c>
-      <c r="K26" s="29" t="n">
+      <c r="K26" s="30" t="n">
         <f aca="false">K25/K19</f>
         <v>0.11251873015873</v>
       </c>
-      <c r="L26" s="29" t="n">
+      <c r="L26" s="30" t="n">
         <f aca="false">L25/L19</f>
         <v>0.135813333333333</v>
       </c>
-      <c r="M26" s="29" t="n">
+      <c r="M26" s="30" t="n">
         <f aca="false">M25/M19</f>
         <v>0.15708231884058</v>
       </c>
-      <c r="N26" s="29" t="n">
+      <c r="N26" s="30" t="n">
         <f aca="false">N25/N19</f>
         <v>0.11251873015873</v>
       </c>
-      <c r="O26" s="19" t="s">
+      <c r="O26" s="20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="24" t="n">
+      <c r="B29" s="25" t="n">
         <f aca="false">SUM(C25:E25)</f>
         <v>583868</v>
       </c>
-      <c r="O29" s="19" t="s">
+      <c r="O29" s="20" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="B32" s="30" t="str">
+      <c r="B32" s="31" t="str">
         <f aca="false">IF(ABS(SUM(C25:N25)-B25)&lt;1,"OK — de tolv månedene summerer seg til årsbudsjettet","AVVIK: månedene og året gir ulikt driftsresultat")</f>
         <v>OK — de tolv månedene summerer seg til årsbudsjettet</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="30" t="str">
+      <c r="B33" s="31" t="str">
         <f aca="false">IF(B25&gt;0,"OK — budsjettet viser overskudd","AVVIK: budsjettet går i minus — da er det ikke likviditeten som er hovedproblemet")</f>
         <v>OK — budsjettet viser overskudd</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B34" s="30" t="str">
+      <c r="B34" s="31" t="str">
         <f aca="false">IF(AND(B8&gt;0,B8&lt;1),"OK — bruttofortjenesten ligger mellom null og hundre prosent","AVVIK: umulig bruttofortjeneste i B8")</f>
         <v>OK — bruttofortjenesten ligger mellom null og hundre prosent</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3129,1910 +3133,1910 @@
   <dimension ref="A1:O90"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" s="20" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <f aca="false">IF($B$5&lt;=30,(30-$B$5)/30,0)</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="20" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="30" t="n">
         <f aca="false">IF($B$5&lt;=30,$B$5/30,MAX(0,(60-$B$5)/30))</f>
         <v>0.666666666666667</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="30" t="n">
         <f aca="false">IF($B$5&lt;=30,0,MIN(1,($B$5-30)/30))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="30" t="n">
         <f aca="false">IF($B$6&lt;=30,(30-$B$6)/30,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="30" t="n">
         <f aca="false">IF($B$6&lt;=30,$B$6/30,MAX(0,(60-$B$6)/30))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <f aca="false">IF($B$6&lt;=30,0,MIN(1,($B$6-30)/30))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="25" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+      <c r="B18" s="26" t="n">
+        <v>982650</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="26" t="n">
         <v>4200000</v>
       </c>
-      <c r="O19" s="19" t="s">
+      <c r="O19" s="20" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="26" t="n">
         <v>2100000</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="26" t="n">
         <v>136000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="26" t="n">
         <v>1064000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="26" t="n">
         <v>890000</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="B25" s="25" t="n">
-        <v>262000</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+      <c r="B25" s="26" t="n">
+        <v>256850</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B26" s="26" t="n">
         <v>192500</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="25" t="n">
+      <c r="B27" s="26" t="n">
         <v>14000</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <v>480000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="B29" s="31" t="n">
+      <c r="B29" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="O29" s="19" t="s">
+      <c r="O29" s="20" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="26" t="n">
         <v>1500000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="26" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>0.08</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="23" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C36" s="27" t="n">
+      <c r="C36" s="28" t="n">
         <f aca="false">(Resultatbudsjett!C7+Resultatbudsjett!D7)*Resultatbudsjett!$B$16</f>
         <v>975000</v>
       </c>
-      <c r="D36" s="27" t="n">
+      <c r="D36" s="28" t="n">
         <f aca="false">(Resultatbudsjett!C9+Resultatbudsjett!D9+2*Resultatbudsjett!$B$15/12+IF(AND($B$29&gt;=1,$B$29&lt;=2),$B$28,0))*Resultatbudsjett!$B$16</f>
         <v>428125</v>
       </c>
-      <c r="E36" s="24" t="n">
+      <c r="E36" s="25" t="n">
         <f aca="false">C36-D36</f>
         <v>546875</v>
       </c>
-      <c r="F36" s="23" t="n">
+      <c r="F36" s="24" t="n">
         <f aca="false">4</f>
         <v>4</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="20" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="C37" s="27" t="n">
+      <c r="C37" s="28" t="n">
         <f aca="false">(Resultatbudsjett!E7+Resultatbudsjett!F7)*Resultatbudsjett!$B$16</f>
         <v>1075000</v>
       </c>
-      <c r="D37" s="27" t="n">
+      <c r="D37" s="28" t="n">
         <f aca="false">(Resultatbudsjett!E9+Resultatbudsjett!F9+2*Resultatbudsjett!$B$15/12+IF(AND($B$29&gt;=3,$B$29&lt;=4),$B$28,0))*Resultatbudsjett!$B$16</f>
         <v>585625</v>
       </c>
-      <c r="E37" s="24" t="n">
+      <c r="E37" s="25" t="n">
         <f aca="false">C37-D37</f>
         <v>489375</v>
       </c>
-      <c r="F37" s="23" t="n">
+      <c r="F37" s="24" t="n">
         <f aca="false">6</f>
         <v>6</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="28" t="n">
         <f aca="false">(Resultatbudsjett!G7+Resultatbudsjett!H7)*Resultatbudsjett!$B$16</f>
         <v>1000000</v>
       </c>
-      <c r="D38" s="27" t="n">
+      <c r="D38" s="28" t="n">
         <f aca="false">(Resultatbudsjett!G9+Resultatbudsjett!H9+2*Resultatbudsjett!$B$15/12+IF(AND($B$29&gt;=5,$B$29&lt;=6),$B$28,0))*Resultatbudsjett!$B$16</f>
         <v>437500</v>
       </c>
-      <c r="E38" s="24" t="n">
+      <c r="E38" s="25" t="n">
         <f aca="false">C38-D38</f>
         <v>562500</v>
       </c>
-      <c r="F38" s="23" t="n">
+      <c r="F38" s="24" t="n">
         <f aca="false">8</f>
         <v>8</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C39" s="28" t="n">
         <f aca="false">(Resultatbudsjett!I7+Resultatbudsjett!J7)*Resultatbudsjett!$B$16</f>
         <v>775000</v>
       </c>
-      <c r="D39" s="27" t="n">
+      <c r="D39" s="28" t="n">
         <f aca="false">(Resultatbudsjett!I9+Resultatbudsjett!J9+2*Resultatbudsjett!$B$15/12+IF(AND($B$29&gt;=7,$B$29&lt;=8),$B$28,0))*Resultatbudsjett!$B$16</f>
         <v>353125</v>
       </c>
-      <c r="E39" s="24" t="n">
+      <c r="E39" s="25" t="n">
         <f aca="false">C39-D39</f>
         <v>421875</v>
       </c>
-      <c r="F39" s="23" t="n">
+      <c r="F39" s="24" t="n">
         <f aca="false">10</f>
         <v>10</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="27" t="n">
+      <c r="C40" s="28" t="n">
         <f aca="false">(Resultatbudsjett!K7+Resultatbudsjett!L7)*Resultatbudsjett!$B$16</f>
         <v>1075000</v>
       </c>
-      <c r="D40" s="27" t="n">
+      <c r="D40" s="28" t="n">
         <f aca="false">(Resultatbudsjett!K9+Resultatbudsjett!L9+2*Resultatbudsjett!$B$15/12+IF(AND($B$29&gt;=9,$B$29&lt;=10),$B$28,0))*Resultatbudsjett!$B$16</f>
         <v>465625</v>
       </c>
-      <c r="E40" s="24" t="n">
+      <c r="E40" s="25" t="n">
         <f aca="false">C40-D40</f>
         <v>609375</v>
       </c>
-      <c r="F40" s="23" t="n">
+      <c r="F40" s="24" t="n">
         <f aca="false">12</f>
         <v>12</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="E43" s="22" t="s">
+      <c r="E43" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="H43" s="22" t="s">
+      <c r="H43" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="I43" s="22" t="s">
+      <c r="I43" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="J43" s="22" t="s">
+      <c r="J43" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="K43" s="22" t="s">
+      <c r="K43" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="L43" s="22" t="s">
+      <c r="L43" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="M43" s="22" t="s">
+      <c r="M43" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="N43" s="22" t="s">
+      <c r="N43" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="O43" s="22" t="s">
+      <c r="O43" s="23" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="23" t="n">
+      <c r="C44" s="24" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="D44" s="23" t="n">
+      <c r="D44" s="24" t="n">
         <f aca="false">2</f>
         <v>2</v>
       </c>
-      <c r="E44" s="23" t="n">
+      <c r="E44" s="24" t="n">
         <f aca="false">3</f>
         <v>3</v>
       </c>
-      <c r="F44" s="23" t="n">
+      <c r="F44" s="24" t="n">
         <f aca="false">4</f>
         <v>4</v>
       </c>
-      <c r="G44" s="23" t="n">
+      <c r="G44" s="24" t="n">
         <f aca="false">5</f>
         <v>5</v>
       </c>
-      <c r="H44" s="23" t="n">
+      <c r="H44" s="24" t="n">
         <f aca="false">6</f>
         <v>6</v>
       </c>
-      <c r="I44" s="23" t="n">
+      <c r="I44" s="24" t="n">
         <f aca="false">7</f>
         <v>7</v>
       </c>
-      <c r="J44" s="23" t="n">
+      <c r="J44" s="24" t="n">
         <f aca="false">8</f>
         <v>8</v>
       </c>
-      <c r="K44" s="23" t="n">
+      <c r="K44" s="24" t="n">
         <f aca="false">9</f>
         <v>9</v>
       </c>
-      <c r="L44" s="23" t="n">
+      <c r="L44" s="24" t="n">
         <f aca="false">10</f>
         <v>10</v>
       </c>
-      <c r="M44" s="23" t="n">
+      <c r="M44" s="24" t="n">
         <f aca="false">11</f>
         <v>11</v>
       </c>
-      <c r="N44" s="23" t="n">
+      <c r="N44" s="24" t="n">
         <f aca="false">12</f>
         <v>12</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="B45" s="27" t="n">
+      <c r="B45" s="28" t="n">
         <f aca="false">SUM(C45:N45)</f>
         <v>24000000</v>
       </c>
-      <c r="C45" s="27" t="n">
+      <c r="C45" s="28" t="n">
         <f aca="false">Resultatbudsjett!C7</f>
         <v>1800000</v>
       </c>
-      <c r="D45" s="27" t="n">
+      <c r="D45" s="28" t="n">
         <f aca="false">Resultatbudsjett!D7</f>
         <v>2100000</v>
       </c>
-      <c r="E45" s="27" t="n">
+      <c r="E45" s="28" t="n">
         <f aca="false">Resultatbudsjett!E7</f>
         <v>2200000</v>
       </c>
-      <c r="F45" s="27" t="n">
+      <c r="F45" s="28" t="n">
         <f aca="false">Resultatbudsjett!F7</f>
         <v>2100000</v>
       </c>
-      <c r="G45" s="27" t="n">
+      <c r="G45" s="28" t="n">
         <f aca="false">Resultatbudsjett!G7</f>
         <v>2000000</v>
       </c>
-      <c r="H45" s="27" t="n">
+      <c r="H45" s="28" t="n">
         <f aca="false">Resultatbudsjett!H7</f>
         <v>2000000</v>
       </c>
-      <c r="I45" s="27" t="n">
+      <c r="I45" s="28" t="n">
         <f aca="false">Resultatbudsjett!I7</f>
         <v>1200000</v>
       </c>
-      <c r="J45" s="27" t="n">
+      <c r="J45" s="28" t="n">
         <f aca="false">Resultatbudsjett!J7</f>
         <v>1900000</v>
       </c>
-      <c r="K45" s="27" t="n">
+      <c r="K45" s="28" t="n">
         <f aca="false">Resultatbudsjett!K7</f>
         <v>2100000</v>
       </c>
-      <c r="L45" s="27" t="n">
+      <c r="L45" s="28" t="n">
         <f aca="false">Resultatbudsjett!L7</f>
         <v>2200000</v>
       </c>
-      <c r="M45" s="27" t="n">
+      <c r="M45" s="28" t="n">
         <f aca="false">Resultatbudsjett!M7</f>
         <v>2300000</v>
       </c>
-      <c r="N45" s="27" t="n">
+      <c r="N45" s="28" t="n">
         <f aca="false">Resultatbudsjett!N7</f>
         <v>2100000</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="B46" s="27" t="n">
+      <c r="B46" s="28" t="n">
         <f aca="false">SUM(C46:N46)</f>
         <v>30000000</v>
       </c>
-      <c r="C46" s="27" t="n">
+      <c r="C46" s="28" t="n">
         <f aca="false">C45*(1+Resultatbudsjett!$B$16)</f>
         <v>2250000</v>
       </c>
-      <c r="D46" s="27" t="n">
+      <c r="D46" s="28" t="n">
         <f aca="false">D45*(1+Resultatbudsjett!$B$16)</f>
         <v>2625000</v>
       </c>
-      <c r="E46" s="27" t="n">
+      <c r="E46" s="28" t="n">
         <f aca="false">E45*(1+Resultatbudsjett!$B$16)</f>
         <v>2750000</v>
       </c>
-      <c r="F46" s="27" t="n">
+      <c r="F46" s="28" t="n">
         <f aca="false">F45*(1+Resultatbudsjett!$B$16)</f>
         <v>2625000</v>
       </c>
-      <c r="G46" s="27" t="n">
+      <c r="G46" s="28" t="n">
         <f aca="false">G45*(1+Resultatbudsjett!$B$16)</f>
         <v>2500000</v>
       </c>
-      <c r="H46" s="27" t="n">
+      <c r="H46" s="28" t="n">
         <f aca="false">H45*(1+Resultatbudsjett!$B$16)</f>
         <v>2500000</v>
       </c>
-      <c r="I46" s="27" t="n">
+      <c r="I46" s="28" t="n">
         <f aca="false">I45*(1+Resultatbudsjett!$B$16)</f>
         <v>1500000</v>
       </c>
-      <c r="J46" s="27" t="n">
+      <c r="J46" s="28" t="n">
         <f aca="false">J45*(1+Resultatbudsjett!$B$16)</f>
         <v>2375000</v>
       </c>
-      <c r="K46" s="27" t="n">
+      <c r="K46" s="28" t="n">
         <f aca="false">K45*(1+Resultatbudsjett!$B$16)</f>
         <v>2625000</v>
       </c>
-      <c r="L46" s="27" t="n">
+      <c r="L46" s="28" t="n">
         <f aca="false">L45*(1+Resultatbudsjett!$B$16)</f>
         <v>2750000</v>
       </c>
-      <c r="M46" s="27" t="n">
+      <c r="M46" s="28" t="n">
         <f aca="false">M45*(1+Resultatbudsjett!$B$16)</f>
         <v>2875000</v>
       </c>
-      <c r="N46" s="27" t="n">
+      <c r="N46" s="28" t="n">
         <f aca="false">N45*(1+Resultatbudsjett!$B$16)</f>
         <v>2625000</v>
       </c>
-      <c r="O46" s="19" t="s">
+      <c r="O46" s="20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="B47" s="27" t="n">
+      <c r="B47" s="28" t="n">
         <f aca="false">SUM(C47:N47)</f>
         <v>28250000</v>
       </c>
-      <c r="C47" s="27" t="n">
+      <c r="C47" s="28" t="n">
         <f aca="false">C46*$B$9</f>
         <v>750000</v>
       </c>
-      <c r="D47" s="27" t="n">
+      <c r="D47" s="28" t="n">
         <f aca="false">D46*$B$9+C46*$B$10</f>
         <v>2375000</v>
       </c>
-      <c r="E47" s="27" t="n">
+      <c r="E47" s="28" t="n">
         <f aca="false">E46*$B$9+D46*$B$10+C46*$B$11</f>
         <v>2666666.66666667</v>
       </c>
-      <c r="F47" s="27" t="n">
+      <c r="F47" s="28" t="n">
         <f aca="false">F46*$B$9+E46*$B$10+D46*$B$11</f>
         <v>2708333.33333333</v>
       </c>
-      <c r="G47" s="27" t="n">
+      <c r="G47" s="28" t="n">
         <f aca="false">G46*$B$9+F46*$B$10+E46*$B$11</f>
         <v>2583333.33333333</v>
       </c>
-      <c r="H47" s="27" t="n">
+      <c r="H47" s="28" t="n">
         <f aca="false">H46*$B$9+G46*$B$10+F46*$B$11</f>
         <v>2500000</v>
       </c>
-      <c r="I47" s="27" t="n">
+      <c r="I47" s="28" t="n">
         <f aca="false">I46*$B$9+H46*$B$10+G46*$B$11</f>
         <v>2166666.66666667</v>
       </c>
-      <c r="J47" s="27" t="n">
+      <c r="J47" s="28" t="n">
         <f aca="false">J46*$B$9+I46*$B$10+H46*$B$11</f>
         <v>1791666.66666667</v>
       </c>
-      <c r="K47" s="27" t="n">
+      <c r="K47" s="28" t="n">
         <f aca="false">K46*$B$9+J46*$B$10+I46*$B$11</f>
         <v>2458333.33333333</v>
       </c>
-      <c r="L47" s="27" t="n">
+      <c r="L47" s="28" t="n">
         <f aca="false">L46*$B$9+K46*$B$10+J46*$B$11</f>
         <v>2666666.66666667</v>
       </c>
-      <c r="M47" s="27" t="n">
+      <c r="M47" s="28" t="n">
         <f aca="false">M46*$B$9+L46*$B$10+K46*$B$11</f>
         <v>2791666.66666667</v>
       </c>
-      <c r="N47" s="27" t="n">
+      <c r="N47" s="28" t="n">
         <f aca="false">N46*$B$9+M46*$B$10+L46*$B$11</f>
         <v>2791666.66666667</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="B48" s="27" t="n">
+      <c r="B48" s="28" t="n">
         <f aca="false">SUM(C48:N48)</f>
         <v>4200000</v>
       </c>
-      <c r="C48" s="27" t="n">
+      <c r="C48" s="28" t="n">
         <f aca="false">$B$19*$B$20</f>
         <v>2520000</v>
       </c>
-      <c r="D48" s="27" t="n">
+      <c r="D48" s="28" t="n">
         <f aca="false">$B$19*(1-$B$20)</f>
         <v>1680000</v>
       </c>
-      <c r="E48" s="27" t="n">
+      <c r="E48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="F48" s="27" t="n">
+      <c r="F48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G48" s="27" t="n">
+      <c r="G48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="H48" s="27" t="n">
+      <c r="H48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="I48" s="27" t="n">
+      <c r="I48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="J48" s="27" t="n">
+      <c r="J48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="K48" s="27" t="n">
+      <c r="K48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="L48" s="27" t="n">
+      <c r="L48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="M48" s="27" t="n">
+      <c r="M48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="N48" s="27" t="n">
+      <c r="N48" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="19" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="B49" s="27" t="n">
+      <c r="B49" s="28" t="n">
         <f aca="false">SUM(C49:N49)</f>
         <v>56000</v>
       </c>
-      <c r="C49" s="27" t="n">
+      <c r="C49" s="28" t="n">
         <f aca="false">IF(MOD(C44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="D49" s="27" t="n">
+      <c r="D49" s="28" t="n">
         <f aca="false">IF(MOD(D44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="27" t="n">
+      <c r="E49" s="28" t="n">
         <f aca="false">IF(MOD(E44,3)=0,$B$27,0)</f>
         <v>14000</v>
       </c>
-      <c r="F49" s="27" t="n">
+      <c r="F49" s="28" t="n">
         <f aca="false">IF(MOD(F44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="G49" s="27" t="n">
+      <c r="G49" s="28" t="n">
         <f aca="false">IF(MOD(G44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="H49" s="27" t="n">
+      <c r="H49" s="28" t="n">
         <f aca="false">IF(MOD(H44,3)=0,$B$27,0)</f>
         <v>14000</v>
       </c>
-      <c r="I49" s="27" t="n">
+      <c r="I49" s="28" t="n">
         <f aca="false">IF(MOD(I44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="27" t="n">
+      <c r="J49" s="28" t="n">
         <f aca="false">IF(MOD(J44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="K49" s="27" t="n">
+      <c r="K49" s="28" t="n">
         <f aca="false">IF(MOD(K44,3)=0,$B$27,0)</f>
         <v>14000</v>
       </c>
-      <c r="L49" s="27" t="n">
+      <c r="L49" s="28" t="n">
         <f aca="false">IF(MOD(L44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="M49" s="27" t="n">
+      <c r="M49" s="28" t="n">
         <f aca="false">IF(MOD(M44,3)=0,$B$27,0)</f>
         <v>0</v>
       </c>
-      <c r="N49" s="27" t="n">
+      <c r="N49" s="28" t="n">
         <f aca="false">IF(MOD(N44,3)=0,$B$27,0)</f>
         <v>14000</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="B50" s="24" t="n">
+      <c r="B50" s="25" t="n">
         <f aca="false">SUM(C50:N50)</f>
         <v>32506000</v>
       </c>
-      <c r="C50" s="24" t="n">
+      <c r="C50" s="25" t="n">
         <f aca="false">SUM(C47:C49)</f>
         <v>3270000</v>
       </c>
-      <c r="D50" s="24" t="n">
+      <c r="D50" s="25" t="n">
         <f aca="false">SUM(D47:D49)</f>
         <v>4055000</v>
       </c>
-      <c r="E50" s="24" t="n">
+      <c r="E50" s="25" t="n">
         <f aca="false">SUM(E47:E49)</f>
         <v>2680666.66666667</v>
       </c>
-      <c r="F50" s="24" t="n">
+      <c r="F50" s="25" t="n">
         <f aca="false">SUM(F47:F49)</f>
         <v>2708333.33333333</v>
       </c>
-      <c r="G50" s="24" t="n">
+      <c r="G50" s="25" t="n">
         <f aca="false">SUM(G47:G49)</f>
         <v>2583333.33333333</v>
       </c>
-      <c r="H50" s="24" t="n">
+      <c r="H50" s="25" t="n">
         <f aca="false">SUM(H47:H49)</f>
         <v>2514000</v>
       </c>
-      <c r="I50" s="24" t="n">
+      <c r="I50" s="25" t="n">
         <f aca="false">SUM(I47:I49)</f>
         <v>2166666.66666667</v>
       </c>
-      <c r="J50" s="24" t="n">
+      <c r="J50" s="25" t="n">
         <f aca="false">SUM(J47:J49)</f>
         <v>1791666.66666667</v>
       </c>
-      <c r="K50" s="24" t="n">
+      <c r="K50" s="25" t="n">
         <f aca="false">SUM(K47:K49)</f>
         <v>2472333.33333333</v>
       </c>
-      <c r="L50" s="24" t="n">
+      <c r="L50" s="25" t="n">
         <f aca="false">SUM(L47:L49)</f>
         <v>2666666.66666667</v>
       </c>
-      <c r="M50" s="24" t="n">
+      <c r="M50" s="25" t="n">
         <f aca="false">SUM(M47:M49)</f>
         <v>2791666.66666667</v>
       </c>
-      <c r="N50" s="24" t="n">
+      <c r="N50" s="25" t="n">
         <f aca="false">SUM(N47:N49)</f>
         <v>2805666.66666667</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="B53" s="27" t="n">
+      <c r="B53" s="28" t="n">
         <f aca="false">SUM(C53:N53)</f>
         <v>9000000</v>
       </c>
-      <c r="C53" s="27" t="n">
+      <c r="C53" s="28" t="n">
         <f aca="false">Resultatbudsjett!C9</f>
         <v>675000</v>
       </c>
-      <c r="D53" s="27" t="n">
+      <c r="D53" s="28" t="n">
         <f aca="false">Resultatbudsjett!D9</f>
         <v>787500</v>
       </c>
-      <c r="E53" s="27" t="n">
+      <c r="E53" s="28" t="n">
         <f aca="false">Resultatbudsjett!E9</f>
         <v>825000</v>
       </c>
-      <c r="F53" s="27" t="n">
+      <c r="F53" s="28" t="n">
         <f aca="false">Resultatbudsjett!F9</f>
         <v>787500</v>
       </c>
-      <c r="G53" s="27" t="n">
+      <c r="G53" s="28" t="n">
         <f aca="false">Resultatbudsjett!G9</f>
         <v>750000</v>
       </c>
-      <c r="H53" s="27" t="n">
+      <c r="H53" s="28" t="n">
         <f aca="false">Resultatbudsjett!H9</f>
         <v>750000</v>
       </c>
-      <c r="I53" s="27" t="n">
+      <c r="I53" s="28" t="n">
         <f aca="false">Resultatbudsjett!I9</f>
         <v>450000</v>
       </c>
-      <c r="J53" s="27" t="n">
+      <c r="J53" s="28" t="n">
         <f aca="false">Resultatbudsjett!J9</f>
         <v>712500</v>
       </c>
-      <c r="K53" s="27" t="n">
+      <c r="K53" s="28" t="n">
         <f aca="false">Resultatbudsjett!K9</f>
         <v>787500</v>
       </c>
-      <c r="L53" s="27" t="n">
+      <c r="L53" s="28" t="n">
         <f aca="false">Resultatbudsjett!L9</f>
         <v>825000</v>
       </c>
-      <c r="M53" s="27" t="n">
+      <c r="M53" s="28" t="n">
         <f aca="false">Resultatbudsjett!M9</f>
         <v>862500</v>
       </c>
-      <c r="N53" s="27" t="n">
+      <c r="N53" s="28" t="n">
         <f aca="false">Resultatbudsjett!N9</f>
         <v>787500</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B54" s="27" t="n">
+      <c r="B54" s="28" t="n">
         <f aca="false">SUM(C54:N54)</f>
         <v>11250000</v>
       </c>
-      <c r="C54" s="27" t="n">
+      <c r="C54" s="28" t="n">
         <f aca="false">C53*(1+Resultatbudsjett!$B$16)</f>
         <v>843750</v>
       </c>
-      <c r="D54" s="27" t="n">
+      <c r="D54" s="28" t="n">
         <f aca="false">D53*(1+Resultatbudsjett!$B$16)</f>
         <v>984375</v>
       </c>
-      <c r="E54" s="27" t="n">
+      <c r="E54" s="28" t="n">
         <f aca="false">E53*(1+Resultatbudsjett!$B$16)</f>
         <v>1031250</v>
       </c>
-      <c r="F54" s="27" t="n">
+      <c r="F54" s="28" t="n">
         <f aca="false">F53*(1+Resultatbudsjett!$B$16)</f>
         <v>984375</v>
       </c>
-      <c r="G54" s="27" t="n">
+      <c r="G54" s="28" t="n">
         <f aca="false">G53*(1+Resultatbudsjett!$B$16)</f>
         <v>937500</v>
       </c>
-      <c r="H54" s="27" t="n">
+      <c r="H54" s="28" t="n">
         <f aca="false">H53*(1+Resultatbudsjett!$B$16)</f>
         <v>937500</v>
       </c>
-      <c r="I54" s="27" t="n">
+      <c r="I54" s="28" t="n">
         <f aca="false">I53*(1+Resultatbudsjett!$B$16)</f>
         <v>562500</v>
       </c>
-      <c r="J54" s="27" t="n">
+      <c r="J54" s="28" t="n">
         <f aca="false">J53*(1+Resultatbudsjett!$B$16)</f>
         <v>890625</v>
       </c>
-      <c r="K54" s="27" t="n">
+      <c r="K54" s="28" t="n">
         <f aca="false">K53*(1+Resultatbudsjett!$B$16)</f>
         <v>984375</v>
       </c>
-      <c r="L54" s="27" t="n">
+      <c r="L54" s="28" t="n">
         <f aca="false">L53*(1+Resultatbudsjett!$B$16)</f>
         <v>1031250</v>
       </c>
-      <c r="M54" s="27" t="n">
+      <c r="M54" s="28" t="n">
         <f aca="false">M53*(1+Resultatbudsjett!$B$16)</f>
         <v>1078125</v>
       </c>
-      <c r="N54" s="27" t="n">
+      <c r="N54" s="28" t="n">
         <f aca="false">N53*(1+Resultatbudsjett!$B$16)</f>
         <v>984375</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="B55" s="27" t="n">
+      <c r="B55" s="28" t="n">
         <f aca="false">SUM(C55:N55)</f>
         <v>12365625</v>
       </c>
-      <c r="C55" s="27" t="n">
+      <c r="C55" s="28" t="n">
         <f aca="false">C54*$B$13+$B$21</f>
         <v>2100000</v>
       </c>
-      <c r="D55" s="27" t="n">
+      <c r="D55" s="28" t="n">
         <f aca="false">D54*$B$13+C54*$B$14</f>
         <v>843750</v>
       </c>
-      <c r="E55" s="27" t="n">
+      <c r="E55" s="28" t="n">
         <f aca="false">E54*$B$13+D54*$B$14+C54*$B$15</f>
         <v>984375</v>
       </c>
-      <c r="F55" s="27" t="n">
+      <c r="F55" s="28" t="n">
         <f aca="false">F54*$B$13+E54*$B$14+D54*$B$15</f>
         <v>1031250</v>
       </c>
-      <c r="G55" s="27" t="n">
+      <c r="G55" s="28" t="n">
         <f aca="false">G54*$B$13+F54*$B$14+E54*$B$15</f>
         <v>984375</v>
       </c>
-      <c r="H55" s="27" t="n">
+      <c r="H55" s="28" t="n">
         <f aca="false">H54*$B$13+G54*$B$14+F54*$B$15</f>
         <v>937500</v>
       </c>
-      <c r="I55" s="27" t="n">
+      <c r="I55" s="28" t="n">
         <f aca="false">I54*$B$13+H54*$B$14+G54*$B$15</f>
         <v>937500</v>
       </c>
-      <c r="J55" s="27" t="n">
+      <c r="J55" s="28" t="n">
         <f aca="false">J54*$B$13+I54*$B$14+H54*$B$15</f>
         <v>562500</v>
       </c>
-      <c r="K55" s="27" t="n">
+      <c r="K55" s="28" t="n">
         <f aca="false">K54*$B$13+J54*$B$14+I54*$B$15</f>
         <v>890625</v>
       </c>
-      <c r="L55" s="27" t="n">
+      <c r="L55" s="28" t="n">
         <f aca="false">L54*$B$13+K54*$B$14+J54*$B$15</f>
         <v>984375</v>
       </c>
-      <c r="M55" s="27" t="n">
+      <c r="M55" s="28" t="n">
         <f aca="false">M54*$B$13+L54*$B$14+K54*$B$15</f>
         <v>1031250</v>
       </c>
-      <c r="N55" s="27" t="n">
+      <c r="N55" s="28" t="n">
         <f aca="false">N54*$B$13+M54*$B$14+L54*$B$15</f>
         <v>1078125</v>
       </c>
-      <c r="O55" s="19" t="s">
+      <c r="O55" s="20" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="B56" s="27" t="n">
+      <c r="B56" s="28" t="n">
         <f aca="false">SUM(C56:N56)</f>
         <v>8400000</v>
       </c>
-      <c r="C56" s="27" t="n">
+      <c r="C56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="D56" s="27" t="n">
+      <c r="D56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="E56" s="27" t="n">
+      <c r="E56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="F56" s="27" t="n">
+      <c r="F56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="G56" s="27" t="n">
+      <c r="G56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="H56" s="27" t="n">
+      <c r="H56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="I56" s="27" t="n">
+      <c r="I56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="J56" s="27" t="n">
+      <c r="J56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="K56" s="27" t="n">
+      <c r="K56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="L56" s="27" t="n">
+      <c r="L56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="M56" s="27" t="n">
+      <c r="M56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
-      <c r="N56" s="27" t="n">
+      <c r="N56" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$10</f>
         <v>700000</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="19" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="B57" s="27" t="n">
+      <c r="B57" s="28" t="n">
         <f aca="false">SUM(C57:N57)</f>
         <v>890000</v>
       </c>
-      <c r="C57" s="27" t="n">
+      <c r="C57" s="28" t="n">
         <f aca="false">IF(C44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="27" t="n">
+      <c r="D57" s="28" t="n">
         <f aca="false">IF(D44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="27" t="n">
+      <c r="E57" s="28" t="n">
         <f aca="false">IF(E44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="F57" s="27" t="n">
+      <c r="F57" s="28" t="n">
         <f aca="false">IF(F44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="G57" s="27" t="n">
+      <c r="G57" s="28" t="n">
         <f aca="false">IF(G44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="H57" s="27" t="n">
+      <c r="H57" s="28" t="n">
         <f aca="false">IF(H44=6,$B$24,0)</f>
         <v>890000</v>
       </c>
-      <c r="I57" s="27" t="n">
+      <c r="I57" s="28" t="n">
         <f aca="false">IF(I44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="27" t="n">
+      <c r="J57" s="28" t="n">
         <f aca="false">IF(J44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="K57" s="27" t="n">
+      <c r="K57" s="28" t="n">
         <f aca="false">IF(K44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="L57" s="27" t="n">
+      <c r="L57" s="28" t="n">
         <f aca="false">IF(L44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="M57" s="27" t="n">
+      <c r="M57" s="28" t="n">
         <f aca="false">IF(M44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="N57" s="27" t="n">
+      <c r="N57" s="28" t="n">
         <f aca="false">IF(N44=6,$B$24,0)</f>
         <v>0</v>
       </c>
-      <c r="O57" s="19" t="s">
+      <c r="O57" s="20" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="19" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="27" t="n">
+      <c r="B58" s="28" t="n">
         <f aca="false">SUM(C58:N58)</f>
         <v>1248490</v>
       </c>
-      <c r="C58" s="27" t="n">
+      <c r="C58" s="28" t="n">
         <f aca="false">IF(C44=1,$B$22,0)+IF(AND(MOD(C44,2)=1,C44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(C44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>136000</v>
       </c>
-      <c r="D58" s="27" t="n">
+      <c r="D58" s="28" t="n">
         <f aca="false">IF(D44=1,$B$22,0)+IF(AND(MOD(D44,2)=1,D44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(D44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="E58" s="27" t="n">
+      <c r="E58" s="28" t="n">
         <f aca="false">IF(E44=1,$B$22,0)+IF(AND(MOD(E44,2)=1,E44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(E44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>197400</v>
       </c>
-      <c r="F58" s="27" t="n">
+      <c r="F58" s="28" t="n">
         <f aca="false">IF(F44=1,$B$22,0)+IF(AND(MOD(F44,2)=1,F44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(F44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="27" t="n">
+      <c r="G58" s="28" t="n">
         <f aca="false">IF(G44=1,$B$22,0)+IF(AND(MOD(G44,2)=1,G44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(G44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>197400</v>
       </c>
-      <c r="H58" s="27" t="n">
+      <c r="H58" s="28" t="n">
         <f aca="false">IF(H44=1,$B$22,0)+IF(AND(MOD(H44,2)=1,H44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(H44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="I58" s="27" t="n">
+      <c r="I58" s="28" t="n">
         <f aca="false">IF(I44=1,$B$22,0)+IF(AND(MOD(I44,2)=1,I44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(I44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>322890</v>
       </c>
-      <c r="J58" s="27" t="n">
+      <c r="J58" s="28" t="n">
         <f aca="false">IF(J44=1,$B$22,0)+IF(AND(MOD(J44,2)=1,J44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(J44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="K58" s="27" t="n">
+      <c r="K58" s="28" t="n">
         <f aca="false">IF(K44=1,$B$22,0)+IF(AND(MOD(K44,2)=1,K44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(K44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>197400</v>
       </c>
-      <c r="L58" s="27" t="n">
+      <c r="L58" s="28" t="n">
         <f aca="false">IF(L44=1,$B$22,0)+IF(AND(MOD(L44,2)=1,L44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(L44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="M58" s="27" t="n">
+      <c r="M58" s="28" t="n">
         <f aca="false">IF(M44=1,$B$22,0)+IF(AND(MOD(M44,2)=1,M44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(M44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>197400</v>
       </c>
-      <c r="N58" s="27" t="n">
+      <c r="N58" s="28" t="n">
         <f aca="false">IF(N44=1,$B$22,0)+IF(AND(MOD(N44,2)=1,N44&gt;=3),2*Resultatbudsjett!$B$10*Resultatbudsjett!$B$12,0)+IF(N44=7,$B$24*Resultatbudsjett!$B$12,0)</f>
         <v>0</v>
       </c>
-      <c r="O58" s="19" t="s">
+      <c r="O58" s="20" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="19" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="B59" s="27" t="n">
+      <c r="B59" s="28" t="n">
         <f aca="false">SUM(C59:N59)</f>
         <v>3694000</v>
       </c>
-      <c r="C59" s="27" t="n">
+      <c r="C59" s="28" t="n">
         <f aca="false">IF(C44=2,$B$23,0)+SUMIF($F$36:$F$40,C44,$E$36:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="D59" s="27" t="n">
+      <c r="D59" s="28" t="n">
         <f aca="false">IF(D44=2,$B$23,0)+SUMIF($F$36:$F$40,D44,$E$36:$E$40)</f>
         <v>1064000</v>
       </c>
-      <c r="E59" s="27" t="n">
+      <c r="E59" s="28" t="n">
         <f aca="false">IF(E44=2,$B$23,0)+SUMIF($F$36:$F$40,E44,$E$36:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="27" t="n">
+      <c r="F59" s="28" t="n">
         <f aca="false">IF(F44=2,$B$23,0)+SUMIF($F$36:$F$40,F44,$E$36:$E$40)</f>
         <v>546875</v>
       </c>
-      <c r="G59" s="27" t="n">
+      <c r="G59" s="28" t="n">
         <f aca="false">IF(G44=2,$B$23,0)+SUMIF($F$36:$F$40,G44,$E$36:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="27" t="n">
+      <c r="H59" s="28" t="n">
         <f aca="false">IF(H44=2,$B$23,0)+SUMIF($F$36:$F$40,H44,$E$36:$E$40)</f>
         <v>489375</v>
       </c>
-      <c r="I59" s="27" t="n">
+      <c r="I59" s="28" t="n">
         <f aca="false">IF(I44=2,$B$23,0)+SUMIF($F$36:$F$40,I44,$E$36:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="J59" s="27" t="n">
+      <c r="J59" s="28" t="n">
         <f aca="false">IF(J44=2,$B$23,0)+SUMIF($F$36:$F$40,J44,$E$36:$E$40)</f>
         <v>562500</v>
       </c>
-      <c r="K59" s="27" t="n">
+      <c r="K59" s="28" t="n">
         <f aca="false">IF(K44=2,$B$23,0)+SUMIF($F$36:$F$40,K44,$E$36:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="L59" s="27" t="n">
+      <c r="L59" s="28" t="n">
         <f aca="false">IF(L44=2,$B$23,0)+SUMIF($F$36:$F$40,L44,$E$36:$E$40)</f>
         <v>421875</v>
       </c>
-      <c r="M59" s="27" t="n">
+      <c r="M59" s="28" t="n">
         <f aca="false">IF(M44=2,$B$23,0)+SUMIF($F$36:$F$40,M44,$E$36:$E$40)</f>
         <v>0</v>
       </c>
-      <c r="N59" s="27" t="n">
+      <c r="N59" s="28" t="n">
         <f aca="false">IF(N44=2,$B$23,0)+SUMIF($F$36:$F$40,N44,$E$36:$E$40)</f>
         <v>609375</v>
       </c>
-      <c r="O59" s="19" t="s">
+      <c r="O59" s="20" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="B60" s="27" t="n">
+      <c r="B60" s="28" t="n">
         <f aca="false">SUM(C60:N60)</f>
         <v>1875000</v>
       </c>
-      <c r="C60" s="27" t="n">
+      <c r="C60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="D60" s="27" t="n">
+      <c r="D60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="E60" s="27" t="n">
+      <c r="E60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="F60" s="27" t="n">
+      <c r="F60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="G60" s="27" t="n">
+      <c r="G60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="H60" s="27" t="n">
+      <c r="H60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="I60" s="27" t="n">
+      <c r="I60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="J60" s="27" t="n">
+      <c r="J60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="K60" s="27" t="n">
+      <c r="K60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="L60" s="27" t="n">
+      <c r="L60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="M60" s="27" t="n">
+      <c r="M60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
-      <c r="N60" s="27" t="n">
+      <c r="N60" s="28" t="n">
         <f aca="false">Resultatbudsjett!$B$15/12*(1+Resultatbudsjett!$B$16)</f>
         <v>156250</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="19" t="s">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B61" s="27" t="n">
+      <c r="B61" s="28" t="n">
         <f aca="false">SUM(C61:N61)</f>
         <v>770000</v>
       </c>
-      <c r="C61" s="27" t="n">
+      <c r="C61" s="28" t="n">
         <f aca="false">IF(MOD(C44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="D61" s="27" t="n">
+      <c r="D61" s="28" t="n">
         <f aca="false">IF(MOD(D44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="27" t="n">
+      <c r="E61" s="28" t="n">
         <f aca="false">IF(MOD(E44,3)=0,$B$26,0)</f>
         <v>192500</v>
       </c>
-      <c r="F61" s="27" t="n">
+      <c r="F61" s="28" t="n">
         <f aca="false">IF(MOD(F44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="G61" s="27" t="n">
+      <c r="G61" s="28" t="n">
         <f aca="false">IF(MOD(G44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H61" s="28" t="n">
         <f aca="false">IF(MOD(H44,3)=0,$B$26,0)</f>
         <v>192500</v>
       </c>
-      <c r="I61" s="27" t="n">
+      <c r="I61" s="28" t="n">
         <f aca="false">IF(MOD(I44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="J61" s="27" t="n">
+      <c r="J61" s="28" t="n">
         <f aca="false">IF(MOD(J44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="K61" s="27" t="n">
+      <c r="K61" s="28" t="n">
         <f aca="false">IF(MOD(K44,3)=0,$B$26,0)</f>
         <v>192500</v>
       </c>
-      <c r="L61" s="27" t="n">
+      <c r="L61" s="28" t="n">
         <f aca="false">IF(MOD(L44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="M61" s="27" t="n">
+      <c r="M61" s="28" t="n">
         <f aca="false">IF(MOD(M44,3)=0,$B$26,0)</f>
         <v>0</v>
       </c>
-      <c r="N61" s="27" t="n">
+      <c r="N61" s="28" t="n">
         <f aca="false">IF(MOD(N44,3)=0,$B$26,0)</f>
         <v>192500</v>
       </c>
-      <c r="O61" s="19" t="s">
+      <c r="O61" s="20" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="19" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B62" s="27" t="n">
+      <c r="B62" s="28" t="n">
         <f aca="false">SUM(C62:N62)</f>
-        <v>262000</v>
-      </c>
-      <c r="C62" s="27" t="n">
+        <v>256850</v>
+      </c>
+      <c r="C62" s="28" t="n">
         <f aca="false">IF(OR(C44=2,C44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="D62" s="27" t="n">
+      <c r="D62" s="28" t="n">
         <f aca="false">IF(OR(D44=2,D44=4),$B$25/2,0)</f>
-        <v>131000</v>
-      </c>
-      <c r="E62" s="27" t="n">
+        <v>128425</v>
+      </c>
+      <c r="E62" s="28" t="n">
         <f aca="false">IF(OR(E44=2,E44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="F62" s="27" t="n">
+      <c r="F62" s="28" t="n">
         <f aca="false">IF(OR(F44=2,F44=4),$B$25/2,0)</f>
-        <v>131000</v>
-      </c>
-      <c r="G62" s="27" t="n">
+        <v>128425</v>
+      </c>
+      <c r="G62" s="28" t="n">
         <f aca="false">IF(OR(G44=2,G44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="H62" s="27" t="n">
+      <c r="H62" s="28" t="n">
         <f aca="false">IF(OR(H44=2,H44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="I62" s="27" t="n">
+      <c r="I62" s="28" t="n">
         <f aca="false">IF(OR(I44=2,I44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="J62" s="27" t="n">
+      <c r="J62" s="28" t="n">
         <f aca="false">IF(OR(J44=2,J44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="K62" s="27" t="n">
+      <c r="K62" s="28" t="n">
         <f aca="false">IF(OR(K44=2,K44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="L62" s="27" t="n">
+      <c r="L62" s="28" t="n">
         <f aca="false">IF(OR(L44=2,L44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="M62" s="27" t="n">
+      <c r="M62" s="28" t="n">
         <f aca="false">IF(OR(M44=2,M44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
-      <c r="N62" s="27" t="n">
+      <c r="N62" s="28" t="n">
         <f aca="false">IF(OR(N44=2,N44=4),$B$25/2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="19" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="27" t="n">
+      <c r="B63" s="28" t="n">
         <f aca="false">SUM(C63:N63)</f>
         <v>600000</v>
       </c>
-      <c r="C63" s="27" t="n">
+      <c r="C63" s="28" t="n">
         <f aca="false">IF(C44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="27" t="n">
+      <c r="D63" s="28" t="n">
         <f aca="false">IF(D44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="27" t="n">
+      <c r="E63" s="28" t="n">
         <f aca="false">IF(E44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>600000</v>
       </c>
-      <c r="F63" s="27" t="n">
+      <c r="F63" s="28" t="n">
         <f aca="false">IF(F44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="G63" s="27" t="n">
+      <c r="G63" s="28" t="n">
         <f aca="false">IF(G44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="H63" s="27" t="n">
+      <c r="H63" s="28" t="n">
         <f aca="false">IF(H44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="I63" s="27" t="n">
+      <c r="I63" s="28" t="n">
         <f aca="false">IF(I44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="J63" s="27" t="n">
+      <c r="J63" s="28" t="n">
         <f aca="false">IF(J44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="K63" s="27" t="n">
+      <c r="K63" s="28" t="n">
         <f aca="false">IF(K44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="L63" s="27" t="n">
+      <c r="L63" s="28" t="n">
         <f aca="false">IF(L44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="M63" s="27" t="n">
+      <c r="M63" s="28" t="n">
         <f aca="false">IF(M44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
-      <c r="N63" s="27" t="n">
+      <c r="N63" s="28" t="n">
         <f aca="false">IF(N44=$B$29,$B$28*(1+Resultatbudsjett!$B$16),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B64" s="24" t="n">
+      <c r="B64" s="25" t="n">
         <f aca="false">SUM(C64:N64)</f>
-        <v>30105115</v>
-      </c>
-      <c r="C64" s="24" t="n">
+        <v>30099965</v>
+      </c>
+      <c r="C64" s="25" t="n">
         <f aca="false">SUM(C55:C63)</f>
         <v>3092250</v>
       </c>
-      <c r="D64" s="24" t="n">
+      <c r="D64" s="25" t="n">
         <f aca="false">SUM(D55:D63)</f>
-        <v>2895000</v>
-      </c>
-      <c r="E64" s="24" t="n">
+        <v>2892425</v>
+      </c>
+      <c r="E64" s="25" t="n">
         <f aca="false">SUM(E55:E63)</f>
         <v>2830525</v>
       </c>
-      <c r="F64" s="24" t="n">
+      <c r="F64" s="25" t="n">
         <f aca="false">SUM(F55:F63)</f>
-        <v>2565375</v>
-      </c>
-      <c r="G64" s="24" t="n">
+        <v>2562800</v>
+      </c>
+      <c r="G64" s="25" t="n">
         <f aca="false">SUM(G55:G63)</f>
         <v>2038025</v>
       </c>
-      <c r="H64" s="24" t="n">
+      <c r="H64" s="25" t="n">
         <f aca="false">SUM(H55:H63)</f>
         <v>3365625</v>
       </c>
-      <c r="I64" s="24" t="n">
+      <c r="I64" s="25" t="n">
         <f aca="false">SUM(I55:I63)</f>
         <v>2116640</v>
       </c>
-      <c r="J64" s="24" t="n">
+      <c r="J64" s="25" t="n">
         <f aca="false">SUM(J55:J63)</f>
         <v>1981250</v>
       </c>
-      <c r="K64" s="24" t="n">
+      <c r="K64" s="25" t="n">
         <f aca="false">SUM(K55:K63)</f>
         <v>2136775</v>
       </c>
-      <c r="L64" s="24" t="n">
+      <c r="L64" s="25" t="n">
         <f aca="false">SUM(L55:L63)</f>
         <v>2262500</v>
       </c>
-      <c r="M64" s="24" t="n">
+      <c r="M64" s="25" t="n">
         <f aca="false">SUM(M55:M63)</f>
         <v>2084900</v>
       </c>
-      <c r="N64" s="24" t="n">
+      <c r="N64" s="25" t="n">
         <f aca="false">SUM(N55:N63)</f>
         <v>2736250</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="17" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="18" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="C67" s="27" t="n">
+      <c r="C67" s="28" t="n">
         <f aca="false">$B$18</f>
-        <v>1000000</v>
-      </c>
-      <c r="D67" s="27" t="n">
+        <v>982650</v>
+      </c>
+      <c r="D67" s="28" t="n">
         <f aca="false">C69</f>
-        <v>1177750</v>
-      </c>
-      <c r="E67" s="27" t="n">
+        <v>1160400</v>
+      </c>
+      <c r="E67" s="28" t="n">
         <f aca="false">D69</f>
-        <v>2337750</v>
-      </c>
-      <c r="F67" s="27" t="n">
+        <v>2322975</v>
+      </c>
+      <c r="F67" s="28" t="n">
         <f aca="false">E69</f>
-        <v>2187891.66666667</v>
-      </c>
-      <c r="G67" s="27" t="n">
+        <v>2173116.66666667</v>
+      </c>
+      <c r="G67" s="28" t="n">
         <f aca="false">F69</f>
-        <v>2330850</v>
-      </c>
-      <c r="H67" s="27" t="n">
+        <v>2318650</v>
+      </c>
+      <c r="H67" s="28" t="n">
         <f aca="false">G69</f>
-        <v>2876158.33333333</v>
-      </c>
-      <c r="I67" s="27" t="n">
+        <v>2863958.33333333</v>
+      </c>
+      <c r="I67" s="28" t="n">
         <f aca="false">H69</f>
-        <v>2024533.33333333</v>
-      </c>
-      <c r="J67" s="27" t="n">
+        <v>2012333.33333333</v>
+      </c>
+      <c r="J67" s="28" t="n">
         <f aca="false">I69</f>
-        <v>2074560</v>
-      </c>
-      <c r="K67" s="27" t="n">
+        <v>2062360</v>
+      </c>
+      <c r="K67" s="28" t="n">
         <f aca="false">J69</f>
-        <v>1884976.66666667</v>
-      </c>
-      <c r="L67" s="27" t="n">
+        <v>1872776.66666667</v>
+      </c>
+      <c r="L67" s="28" t="n">
         <f aca="false">K69</f>
-        <v>2220535</v>
-      </c>
-      <c r="M67" s="27" t="n">
+        <v>2208335</v>
+      </c>
+      <c r="M67" s="28" t="n">
         <f aca="false">L69</f>
-        <v>2624701.66666667</v>
-      </c>
-      <c r="N67" s="27" t="n">
+        <v>2612501.66666667</v>
+      </c>
+      <c r="N67" s="28" t="n">
         <f aca="false">M69</f>
-        <v>3331468.33333333</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="19" t="s">
+        <v>3319268.33333333</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="B68" s="27" t="n">
+      <c r="B68" s="28" t="n">
         <f aca="false">SUM(C68:N68)</f>
-        <v>2400885</v>
-      </c>
-      <c r="C68" s="27" t="n">
+        <v>2406035</v>
+      </c>
+      <c r="C68" s="28" t="n">
         <f aca="false">C50-C64</f>
         <v>177750</v>
       </c>
-      <c r="D68" s="27" t="n">
+      <c r="D68" s="28" t="n">
         <f aca="false">D50-D64</f>
-        <v>1160000</v>
-      </c>
-      <c r="E68" s="27" t="n">
+        <v>1162575</v>
+      </c>
+      <c r="E68" s="28" t="n">
         <f aca="false">E50-E64</f>
         <v>-149858.333333334</v>
       </c>
-      <c r="F68" s="27" t="n">
+      <c r="F68" s="28" t="n">
         <f aca="false">F50-F64</f>
-        <v>142958.333333333</v>
-      </c>
-      <c r="G68" s="27" t="n">
+        <v>145533.333333333</v>
+      </c>
+      <c r="G68" s="28" t="n">
         <f aca="false">G50-G64</f>
         <v>545308.333333333</v>
       </c>
-      <c r="H68" s="27" t="n">
+      <c r="H68" s="28" t="n">
         <f aca="false">H50-H64</f>
         <v>-851625</v>
       </c>
-      <c r="I68" s="27" t="n">
+      <c r="I68" s="28" t="n">
         <f aca="false">I50-I64</f>
         <v>50026.6666666665</v>
       </c>
-      <c r="J68" s="27" t="n">
+      <c r="J68" s="28" t="n">
         <f aca="false">J50-J64</f>
         <v>-189583.333333334</v>
       </c>
-      <c r="K68" s="27" t="n">
+      <c r="K68" s="28" t="n">
         <f aca="false">K50-K64</f>
         <v>335558.333333333</v>
       </c>
-      <c r="L68" s="27" t="n">
+      <c r="L68" s="28" t="n">
         <f aca="false">L50-L64</f>
         <v>404166.666666667</v>
       </c>
-      <c r="M68" s="27" t="n">
+      <c r="M68" s="28" t="n">
         <f aca="false">M50-M64</f>
         <v>706766.666666667</v>
       </c>
-      <c r="N68" s="27" t="n">
+      <c r="N68" s="28" t="n">
         <f aca="false">N50-N64</f>
         <v>69416.6666666665</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="C69" s="24" t="n">
+      <c r="C69" s="25" t="n">
         <f aca="false">C67+C68</f>
-        <v>1177750</v>
-      </c>
-      <c r="D69" s="24" t="n">
+        <v>1160400</v>
+      </c>
+      <c r="D69" s="25" t="n">
         <f aca="false">D67+D68</f>
-        <v>2337750</v>
-      </c>
-      <c r="E69" s="24" t="n">
+        <v>2322975</v>
+      </c>
+      <c r="E69" s="25" t="n">
         <f aca="false">E67+E68</f>
-        <v>2187891.66666667</v>
-      </c>
-      <c r="F69" s="24" t="n">
+        <v>2173116.66666667</v>
+      </c>
+      <c r="F69" s="25" t="n">
         <f aca="false">F67+F68</f>
-        <v>2330850</v>
-      </c>
-      <c r="G69" s="24" t="n">
+        <v>2318650</v>
+      </c>
+      <c r="G69" s="25" t="n">
         <f aca="false">G67+G68</f>
-        <v>2876158.33333333</v>
-      </c>
-      <c r="H69" s="24" t="n">
+        <v>2863958.33333333</v>
+      </c>
+      <c r="H69" s="25" t="n">
         <f aca="false">H67+H68</f>
-        <v>2024533.33333333</v>
-      </c>
-      <c r="I69" s="24" t="n">
+        <v>2012333.33333333</v>
+      </c>
+      <c r="I69" s="25" t="n">
         <f aca="false">I67+I68</f>
-        <v>2074560</v>
-      </c>
-      <c r="J69" s="24" t="n">
+        <v>2062360</v>
+      </c>
+      <c r="J69" s="25" t="n">
         <f aca="false">J67+J68</f>
-        <v>1884976.66666667</v>
-      </c>
-      <c r="K69" s="24" t="n">
+        <v>1872776.66666667</v>
+      </c>
+      <c r="K69" s="25" t="n">
         <f aca="false">K67+K68</f>
-        <v>2220535</v>
-      </c>
-      <c r="L69" s="24" t="n">
+        <v>2208335</v>
+      </c>
+      <c r="L69" s="25" t="n">
         <f aca="false">L67+L68</f>
-        <v>2624701.66666667</v>
-      </c>
-      <c r="M69" s="24" t="n">
+        <v>2612501.66666667</v>
+      </c>
+      <c r="M69" s="25" t="n">
         <f aca="false">M67+M68</f>
-        <v>3331468.33333333</v>
-      </c>
-      <c r="N69" s="24" t="n">
+        <v>3319268.33333333</v>
+      </c>
+      <c r="N69" s="25" t="n">
         <f aca="false">N67+N68</f>
-        <v>3400885</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="19" t="s">
+        <v>3388685</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="C70" s="27" t="n">
+      <c r="C70" s="28" t="n">
         <f aca="false">MAX(0,-C69)</f>
         <v>0</v>
       </c>
-      <c r="D70" s="27" t="n">
+      <c r="D70" s="28" t="n">
         <f aca="false">MAX(0,-D69)</f>
         <v>0</v>
       </c>
-      <c r="E70" s="27" t="n">
+      <c r="E70" s="28" t="n">
         <f aca="false">MAX(0,-E69)</f>
         <v>0</v>
       </c>
-      <c r="F70" s="27" t="n">
+      <c r="F70" s="28" t="n">
         <f aca="false">MAX(0,-F69)</f>
         <v>0</v>
       </c>
-      <c r="G70" s="27" t="n">
+      <c r="G70" s="28" t="n">
         <f aca="false">MAX(0,-G69)</f>
         <v>0</v>
       </c>
-      <c r="H70" s="27" t="n">
+      <c r="H70" s="28" t="n">
         <f aca="false">MAX(0,-H69)</f>
         <v>0</v>
       </c>
-      <c r="I70" s="27" t="n">
+      <c r="I70" s="28" t="n">
         <f aca="false">MAX(0,-I69)</f>
         <v>0</v>
       </c>
-      <c r="J70" s="27" t="n">
+      <c r="J70" s="28" t="n">
         <f aca="false">MAX(0,-J69)</f>
         <v>0</v>
       </c>
-      <c r="K70" s="27" t="n">
+      <c r="K70" s="28" t="n">
         <f aca="false">MAX(0,-K69)</f>
         <v>0</v>
       </c>
-      <c r="L70" s="27" t="n">
+      <c r="L70" s="28" t="n">
         <f aca="false">MAX(0,-L69)</f>
         <v>0</v>
       </c>
-      <c r="M70" s="27" t="n">
+      <c r="M70" s="28" t="n">
         <f aca="false">MAX(0,-M69)</f>
         <v>0</v>
       </c>
-      <c r="N70" s="27" t="n">
+      <c r="N70" s="28" t="n">
         <f aca="false">MAX(0,-N69)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="17" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="18" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="B73" s="24" t="n">
+      <c r="B73" s="25" t="n">
         <f aca="false">MIN(C69:N69)</f>
-        <v>1177750</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="19" t="s">
+        <v>1160400</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="B74" s="32" t="str">
+      <c r="B74" s="33" t="str">
         <f aca="false">INDEX($C$43:$N$43,MATCH(MIN(C69:N69),C69:N69,0))</f>
         <v>Jan</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="19" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="B75" s="23" t="n">
+      <c r="B75" s="24" t="n">
         <f aca="false">COUNTIF(C69:N69,"&lt;0")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="19" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="B76" s="27" t="n">
+      <c r="B76" s="28" t="n">
         <f aca="false">MAX(C70:N70)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="19" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B77" s="27" t="n">
+      <c r="B77" s="28" t="n">
         <f aca="false">B76+B31</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="19" t="s">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="B78" s="28" t="n">
+      <c r="B78" s="29" t="n">
         <f aca="false">B77/B30</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="19" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B79" s="27" t="n">
+      <c r="B79" s="28" t="n">
         <f aca="false">SUM(C70:N70)/12*B32</f>
         <v>0</v>
       </c>
-      <c r="O79" s="19" t="s">
+      <c r="O79" s="20" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="19" t="s">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="B80" s="27" t="n">
+      <c r="B80" s="28" t="n">
         <f aca="false">Resultatbudsjett!B25</f>
         <v>2085472</v>
       </c>
-      <c r="O80" s="19" t="s">
+      <c r="O80" s="20" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="17" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="18" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="19" t="s">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="B83" s="30" t="str">
+      <c r="B83" s="31" t="str">
         <f aca="false">IF(AND(ABS(B9+B10+B11-1)&lt;0.0001,ABS(B13+B14+B15-1)&lt;0.0001),"OK — alt salg og alle varekjøp blir betalt til slutt","AVVIK: andelene summerer seg ikke til hundre prosent — kredittiden må ligge mellom 0 og 60 dager")</f>
         <v>OK — alt salg og alle varekjøp blir betalt til slutt</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="19" t="s">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="B84" s="30" t="str">
+      <c r="B84" s="31" t="str">
         <f aca="false">IF(B47&lt;=B46+1,"OK — innbetalingene overstiger ikke det som er fakturert","AVVIK: mer er innbetalt enn fakturert")</f>
         <v>OK — innbetalingene overstiger ikke det som er fakturert</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="19" t="s">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="B85" s="30" t="str">
+      <c r="B85" s="31" t="str">
         <f aca="false">IF(ABS(N69-(B18+SUM(C68:N68)))&lt;1,"OK — utgående beholdning er inngående pluss alle endringene","AVVIK: beholdningen henger ikke sammen")</f>
         <v>OK — utgående beholdning er inngående pluss alle endringene</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="19" t="s">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="B86" s="30" t="str">
+      <c r="B86" s="31" t="str">
         <f aca="false">IF(B77&lt;=B30,"OK — trekket holder seg innenfor rammen, men se hvor mye av den som er brukt opp i B78","AVVIK: rammen sprenges — banken må kontaktes FØR det skjer, ikke etter")</f>
         <v>OK — trekket holder seg innenfor rammen, men se hvor mye av den som er brukt opp i B78</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="19" t="s">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="B87" s="30" t="str">
+      <c r="B87" s="31" t="str">
         <f aca="false">IF(ABS(B80-Resultatbudsjett!B25)&lt;1,"OK — driftsresultatet står stille uansett hva du setter i B5. Resultat og likviditet er to ulike spørsmål","AVVIK: her er noe koblet feil")</f>
         <v>OK — driftsresultatet står stille uansett hva du setter i B5. Resultat og likviditet er to ulike spørsmål</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="21" t="s">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="22" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="16" t="s">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="17" t="s">
         <v>249</v>
       </c>
     </row>
@@ -5080,349 +5084,349 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="23" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="26" t="n">
         <v>22000000</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <v>22400000</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="25" t="n">
         <f aca="false">C6-B6</f>
         <v>400000</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="30" t="n">
         <f aca="false">D6/B6</f>
         <v>0.0181818181818182</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="20" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <v>8240000</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <v>8390000</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="25" t="n">
         <f aca="false">B7-C7</f>
         <v>-150000</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="30" t="n">
         <f aca="false">D7/B7</f>
         <v>-0.0182038834951456</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="30" t="n">
         <f aca="false">B7/$B$6</f>
         <v>0.374545454545455</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="30" t="n">
         <f aca="false">C7/$C$6</f>
         <v>0.374553571428571</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <v>10460000</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <v>10660000</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="25" t="n">
         <f aca="false">B8-C8</f>
         <v>-200000</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <f aca="false">D8/B8</f>
         <v>-0.0191204588910134</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="30" t="n">
         <f aca="false">B8/$B$6</f>
         <v>0.475454545454545</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="30" t="n">
         <f aca="false">C8/$C$6</f>
         <v>0.475892857142857</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="20" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <v>640000</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <v>620000</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="25" t="n">
         <f aca="false">B9-C9</f>
         <v>20000</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <f aca="false">D9/B9</f>
         <v>0.03125</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="30" t="n">
         <f aca="false">B9/$B$6</f>
         <v>0.0290909090909091</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="30" t="n">
         <f aca="false">C9/$C$6</f>
         <v>0.0276785714285714</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="20" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <v>1250000</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <v>1386000</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="25" t="n">
         <f aca="false">B10-C10</f>
         <v>-136000</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="30" t="n">
         <f aca="false">D10/B10</f>
         <v>-0.1088</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="30" t="n">
         <f aca="false">B10/$B$6</f>
         <v>0.0568181818181818</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="30" t="n">
         <f aca="false">C10/$C$6</f>
         <v>0.061875</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="20" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <f aca="false">SUM(B7:B10)</f>
         <v>20590000</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <f aca="false">SUM(C7:C10)</f>
         <v>21056000</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">B12-C12</f>
         <v>-466000</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="30" t="n">
         <f aca="false">D12/B12</f>
         <v>-0.0226323457989315</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <f aca="false">B6-B12</f>
         <v>1410000</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <f aca="false">C6-C12</f>
         <v>1344000</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <f aca="false">C13-B13</f>
         <v>-66000</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="30" t="n">
         <f aca="false">D13/B13</f>
         <v>-0.0468085106382979</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="20" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="28" t="n">
         <f aca="false">C6-B6</f>
         <v>400000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <f aca="false">C6*F7</f>
         <v>8389818.18181818</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="28" t="n">
         <f aca="false">C7</f>
         <v>8390000</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="25" t="n">
         <f aca="false">B17-B18</f>
         <v>-181.818181818351</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="20" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="28" t="n">
         <f aca="false">C6*F10</f>
         <v>1272727.27272727</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="28" t="n">
         <f aca="false">C10</f>
         <v>1386000</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="25" t="n">
         <f aca="false">B20-B21</f>
         <v>-113272.727272727</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="20" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="B25" s="30" t="str">
+      <c r="B25" s="31" t="str">
         <f aca="false">IF(D6&gt;0,"OK — bedriften solgte mer enn planlagt. Da MÅ varekostnaden og lønnskostnaden også være høyere","AVVIK: salget sviktet — da er kostnadsavvikene en annen historie")</f>
         <v>OK — bedriften solgte mer enn planlagt. Da MÅ varekostnaden og lønnskostnaden også være høyere</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="B26" s="30" t="str">
+      <c r="B26" s="31" t="str">
         <f aca="false">IF(ABS(F7-G7)&lt;0.01,"OK — varekostnaden utgjør nesten nøyaktig samme andel av salget som budsjettert. Innkjøpet har gått som planlagt","AVVIK: varekostnadsandelen har flyttet seg — da er det et prisavvik, og da er innkjøperen riktig adressat")</f>
         <v>OK — varekostnaden utgjør nesten nøyaktig samme andel av salget som budsjettert. Innkjøpet har gått som planlagt</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="B27" s="30" t="str">
+      <c r="B27" s="31" t="str">
         <f aca="false">IF(ABS(G10-F10)&gt;ABS(G7-F7),"OK — andre driftskostnader har flyttet seg mest som andel av salget. Det er der Kari skal be om en spesifikasjon","AVVIK: her er det varekostnaden som har flyttet seg mest")</f>
         <v>OK — andre driftskostnader har flyttet seg mest som andel av salget. Det er der Kari skal be om en spesifikasjon</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
         <v>282</v>
       </c>
     </row>
@@ -5460,459 +5464,460 @@
   <dimension ref="A1:F53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="33" t="n">
+      <c r="B7" s="34" t="n">
         <f aca="false">Likviditet!B5</f>
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="25" t="n">
         <f aca="false">Likviditet!B73</f>
-        <v>1177750</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+        <v>1160400</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="20" t="str">
+      <c r="B9" s="21" t="str">
         <f aca="false">Likviditet!B74</f>
         <v>Jan</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="24" t="n">
         <f aca="false">Likviditet!B75</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="28" t="n">
         <f aca="false">Resultatbudsjett!B25</f>
         <v>2085472</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22" t="s">
+      <c r="D13" s="23"/>
+      <c r="E13" s="23" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="31" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="C14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="19" t="s">
+      <c r="C14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="C15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="19" t="s">
+      <c r="C15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="C16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="19" t="s">
+      <c r="C16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="C17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="19" t="s">
+      <c r="C17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="32" t="n">
         <v>54</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="19" t="s">
+      <c r="C18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22" t="s">
+      <c r="D24" s="23"/>
+      <c r="E24" s="23" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="C25" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="19" t="s">
+      <c r="C25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="C26" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="19" t="s">
+      <c r="C26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="20" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="C27" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="19" t="s">
+      <c r="C27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="C28" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="19" t="s">
+      <c r="C28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="23" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C35" s="31" t="n">
+      <c r="C35" s="32" t="n">
         <v>54</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="24" t="n">
         <f aca="false">C35-B35</f>
         <v>34</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="20" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B36" s="26" t="n">
         <v>10005666.6666667</v>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C36" s="26" t="n">
         <v>6989000</v>
       </c>
-      <c r="D36" s="24" t="n">
+      <c r="D36" s="25" t="n">
         <f aca="false">C36-B36</f>
-        <v>-3016666.66666667</v>
-      </c>
-      <c r="E36" s="19" t="s">
+        <v>-3016666.6666667</v>
+      </c>
+      <c r="E36" s="20" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B37" s="25" t="n">
-        <v>8817775</v>
-      </c>
-      <c r="C37" s="27" t="n">
+      <c r="B37" s="26" t="n">
+        <f aca="false">SUM(Likviditet!C64:E64)</f>
+        <v>8815200</v>
+      </c>
+      <c r="C37" s="28" t="n">
         <f aca="false">B37</f>
-        <v>8817775</v>
-      </c>
-      <c r="D37" s="27" t="n">
+        <v>8815200</v>
+      </c>
+      <c r="D37" s="28" t="n">
         <f aca="false">C37-B37</f>
         <v>0</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="20" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="B38" s="24" t="n">
+      <c r="B38" s="25" t="n">
         <f aca="false">Likviditet!B18+B36-B37</f>
-        <v>2187891.66666667</v>
-      </c>
-      <c r="C38" s="24" t="n">
+        <v>2173116.6666667</v>
+      </c>
+      <c r="C38" s="25" t="n">
         <f aca="false">Likviditet!B18+C36-C37</f>
-        <v>-828775</v>
-      </c>
-      <c r="D38" s="24" t="n">
+        <v>-843550</v>
+      </c>
+      <c r="D38" s="25" t="n">
         <f aca="false">C38-B38</f>
-        <v>-3016666.66666667</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+        <v>-3016666.6666667</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="B39" s="27" t="n">
+      <c r="B39" s="28" t="n">
         <f aca="false">Resultatbudsjett!B29</f>
         <v>583868</v>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C39" s="28" t="n">
         <f aca="false">B39</f>
         <v>583868</v>
       </c>
-      <c r="D39" s="27" t="n">
+      <c r="D39" s="28" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="20" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="19" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="B42" s="27" t="n">
+      <c r="B42" s="28" t="n">
         <f aca="false">Likviditet!B19</f>
         <v>4200000</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="B43" s="25" t="n">
+      <c r="B43" s="26" t="n">
         <v>28000000</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="B44" s="34" t="n">
+      <c r="B44" s="35" t="n">
         <f aca="false">B42*360/B43</f>
         <v>54</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="B45" s="35" t="n">
+      <c r="B45" s="36" t="n">
         <f aca="false">B35</f>
         <v>20</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="B46" s="34" t="n">
+      <c r="B46" s="35" t="n">
         <f aca="false">B44-B45</f>
         <v>34</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="20" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="19" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B49" s="30" t="str">
+      <c r="B49" s="31" t="str">
         <f aca="false">IF(ABS(D38-D36)&lt;1,"OK — hele avviket kommer fra innbetalingene. Utbetalingene er de samme","AVVIK: da er det mer enn kredittiden som har endret seg")</f>
         <v>OK — hele avviket kommer fra innbetalingene. Utbetalingene er de samme</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="19" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="B50" s="30" t="str">
+      <c r="B50" s="31" t="str">
         <f aca="false">IF(B39&gt;0,"OK — resultatbudsjettet viser overskudd i et kvartal der kontoen gikk tom. Det er hele poenget i kapitlet","AVVIK: går resultatet også i minus, er dette et lønnsomhetsproblem og ikke bare et likviditetsproblem")</f>
         <v>OK — resultatbudsjettet viser overskudd i et kvartal der kontoen gikk tom. Det er hele poenget i kapitlet</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="B51" s="30" t="str">
+      <c r="B51" s="31" t="str">
         <f aca="false">IF(B46&gt;0,"OK — regnskapet for 2026 viste lengre kredittid enn budsjettet forutsatte. Bommen var mulig å se i november","AVVIK: budsjettet var i tråd med regnskapet — da må forklaringen ligge et annet sted")</f>
         <v>OK — regnskapet for 2026 viste lengre kredittid enn budsjettet forutsatte. Bommen var mulig å se i november</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="s">
         <v>347</v>
       </c>
     </row>

--- a/pensum/ok09/OK09_Budsjettering_Regneark_Budsjett.xlsx
+++ b/pensum/ok09/OK09_Budsjettering_Regneark_Budsjett.xlsx
@@ -1278,7 +1278,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1425,6 +1425,14 @@
     </xf>
     <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1748,7 +1756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
@@ -3283,16 +3291,16 @@
         <v>2100000</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+    <row ht="27" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A22" t="s">
         <v>173</v>
       </c>
       <c r="B22" s="26" t="n">
         <v>136000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    <row ht="27" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A23" t="s">
         <v>174</v>
       </c>
       <c r="B23" s="26" t="n">
@@ -3307,8 +3315,8 @@
         <v>890000</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+    <row ht="27" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A25" t="s">
         <v>176</v>
       </c>
       <c r="B25" s="26" t="n">
@@ -4938,8 +4946,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="20" t="s">
+    <row ht="27" customHeight="true" r="77" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A77" t="s">
         <v>237</v>
       </c>
       <c r="B77" s="28" t="n">
@@ -5012,8 +5020,8 @@
         <v>OK — utgående beholdning er inngående pluss alle endringene</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="20" t="s">
+    <row ht="27" customHeight="true" r="86" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A86" t="s">
         <v>246</v>
       </c>
       <c r="B86" s="31" t="str">
@@ -5101,7 +5109,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
         <v>103</v>
       </c>
@@ -5328,8 +5336,8 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+    <row ht="27" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A17" t="s">
         <v>270</v>
       </c>
       <c r="B17" s="28" t="n">
@@ -5358,8 +5366,8 @@
         <v>273</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
+    <row ht="27" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="37" r="A20" t="s">
         <v>274</v>
       </c>
       <c r="B20" s="28" t="n">
@@ -5376,8 +5384,8 @@
         <v>1386000</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
+    <row ht="27" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A22" t="s">
         <v>276</v>
       </c>
       <c r="B22" s="25" t="n">
@@ -5538,7 +5546,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
         <v>290</v>
       </c>
@@ -5653,11 +5661,11 @@
         <v>310</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c s="37" r="B25" t="s">
         <v>312</v>
       </c>
       <c r="C25" s="26" t="n">
@@ -5667,11 +5675,11 @@
         <v>313</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c s="37" r="B26" t="s">
         <v>315</v>
       </c>
       <c r="C26" s="26" t="n">
@@ -5681,11 +5689,11 @@
         <v>316</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c s="37" r="B27" t="s">
         <v>318</v>
       </c>
       <c r="C27" s="26" t="n">
@@ -5695,11 +5703,11 @@
         <v>319</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c s="37" r="B28" t="s">
         <v>321</v>
       </c>
       <c r="C28" s="26" t="n">
